--- a/benchmark_results/benchmark_comparison.xlsx
+++ b/benchmark_results/benchmark_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2910,6 +2910,594 @@
       </c>
       <c r="Z29" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>img_0225.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>76</v>
+      </c>
+      <c r="D30" t="n">
+        <v>75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>18</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>71</v>
+      </c>
+      <c r="M30" t="n">
+        <v>81</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>173</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>189</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>img_0056.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>44</v>
+      </c>
+      <c r="M31" t="n">
+        <v>38</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>img_0308.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>36</v>
+      </c>
+      <c r="D32" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>47</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P32" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>113</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>img_0023.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>48</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>83</v>
+      </c>
+      <c r="M33" t="n">
+        <v>89</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>191</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>img_0291.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>36</v>
+      </c>
+      <c r="D34" t="n">
+        <v>37</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>30</v>
+      </c>
+      <c r="N34" t="n">
+        <v>20</v>
+      </c>
+      <c r="O34" t="n">
+        <v>45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-19</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>114</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>img_0076.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>37</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-23</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>v8s_640</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>img_0292.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24</v>
+      </c>
+      <c r="M36" t="n">
+        <v>31</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/benchmark_results/benchmark_comparison.xlsx
+++ b/benchmark_results/benchmark_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2322,1182 +2322,6 @@
       </c>
       <c r="Z22" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>img_0225.jpg</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>76</v>
-      </c>
-      <c r="D23" t="n">
-        <v>80</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>71</v>
-      </c>
-      <c r="M23" t="n">
-        <v>82</v>
-      </c>
-      <c r="N23" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>173</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>202</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>img_0056.jpg</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>40</v>
-      </c>
-      <c r="G24" t="n">
-        <v>14</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-26</v>
-      </c>
-      <c r="I24" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>44</v>
-      </c>
-      <c r="M24" t="n">
-        <v>51</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7</v>
-      </c>
-      <c r="S24" t="n">
-        <v>6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>107</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>img_0308.jpg</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>36</v>
-      </c>
-      <c r="D25" t="n">
-        <v>30</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" t="n">
-        <v>10</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" t="n">
-        <v>10</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>33</v>
-      </c>
-      <c r="M25" t="n">
-        <v>45</v>
-      </c>
-      <c r="N25" t="n">
-        <v>12</v>
-      </c>
-      <c r="O25" t="n">
-        <v>10</v>
-      </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>101</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>105</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>img_0023.jpg</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>75</v>
-      </c>
-      <c r="D26" t="n">
-        <v>62</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F26" t="n">
-        <v>18</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>83</v>
-      </c>
-      <c r="M26" t="n">
-        <v>86</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" t="n">
-        <v>8</v>
-      </c>
-      <c r="P26" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>191</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>176</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>img_0291.jpg</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>36</v>
-      </c>
-      <c r="D27" t="n">
-        <v>35</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>13</v>
-      </c>
-      <c r="G27" t="n">
-        <v>14</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>10</v>
-      </c>
-      <c r="M27" t="n">
-        <v>26</v>
-      </c>
-      <c r="N27" t="n">
-        <v>16</v>
-      </c>
-      <c r="O27" t="n">
-        <v>45</v>
-      </c>
-      <c r="P27" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-13</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>116</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>img_0076.jpg</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>37</v>
-      </c>
-      <c r="D28" t="n">
-        <v>14</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-23</v>
-      </c>
-      <c r="F28" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>9</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>82</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>-38</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>v8s_800_local</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>img_0292.jpg</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" t="n">
-        <v>20</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>24</v>
-      </c>
-      <c r="M29" t="n">
-        <v>33</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>8</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>67</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>img_0225.jpg</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>76</v>
-      </c>
-      <c r="D30" t="n">
-        <v>75</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>15</v>
-      </c>
-      <c r="G30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>71</v>
-      </c>
-      <c r="M30" t="n">
-        <v>81</v>
-      </c>
-      <c r="N30" t="n">
-        <v>10</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>6</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>173</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>189</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>img_0056.jpg</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="n">
-        <v>40</v>
-      </c>
-      <c r="G31" t="n">
-        <v>13</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>44</v>
-      </c>
-      <c r="M31" t="n">
-        <v>38</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>107</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>img_0308.jpg</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>36</v>
-      </c>
-      <c r="D32" t="n">
-        <v>31</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>9</v>
-      </c>
-      <c r="G32" t="n">
-        <v>12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>33</v>
-      </c>
-      <c r="M32" t="n">
-        <v>47</v>
-      </c>
-      <c r="N32" t="n">
-        <v>14</v>
-      </c>
-      <c r="O32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P32" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>101</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>113</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>img_0023.jpg</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>75</v>
-      </c>
-      <c r="D33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-27</v>
-      </c>
-      <c r="F33" t="n">
-        <v>18</v>
-      </c>
-      <c r="G33" t="n">
-        <v>13</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>83</v>
-      </c>
-      <c r="M33" t="n">
-        <v>89</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>191</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>155</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>-36</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>img_0291.jpg</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>36</v>
-      </c>
-      <c r="D34" t="n">
-        <v>37</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>13</v>
-      </c>
-      <c r="G34" t="n">
-        <v>13</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>10</v>
-      </c>
-      <c r="M34" t="n">
-        <v>30</v>
-      </c>
-      <c r="N34" t="n">
-        <v>20</v>
-      </c>
-      <c r="O34" t="n">
-        <v>45</v>
-      </c>
-      <c r="P34" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-19</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>114</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>img_0076.jpg</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>37</v>
-      </c>
-      <c r="D35" t="n">
-        <v>12</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F35" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" t="n">
-        <v>8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="n">
-        <v>-23</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>v8s_640</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>img_0292.jpg</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>20</v>
-      </c>
-      <c r="D36" t="n">
-        <v>22</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>24</v>
-      </c>
-      <c r="M36" t="n">
-        <v>31</v>
-      </c>
-      <c r="N36" t="n">
-        <v>7</v>
-      </c>
-      <c r="O36" t="n">
-        <v>8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
